--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,60 +1587,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119624174</v>
+        <v>137022561</v>
       </c>
       <c r="B10" t="n">
-        <v>57966</v>
+        <v>81138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>6444</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579371</v>
+        <v>579398</v>
       </c>
       <c r="R10" t="n">
-        <v>6398423</v>
+        <v>6398145</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,17 +1652,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,44 +1672,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624174</t>
+          <t>https://artportalen.se/Sighting/137022561</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118608477</v>
+        <v>119624174</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1734,25 +1717,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579312</v>
+        <v>579371</v>
       </c>
       <c r="R11" t="n">
-        <v>6398154</v>
+        <v>6398423</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,22 +1766,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,24 +1791,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/119624174</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118609828</v>
+        <v>118608477</v>
       </c>
       <c r="B12" t="n">
         <v>57950</v>
@@ -1863,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579427</v>
+        <v>579312</v>
       </c>
       <c r="R12" t="n">
-        <v>6398257</v>
+        <v>6398154</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1898,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,13 +1919,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609828</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118610366</v>
+        <v>118609828</v>
       </c>
       <c r="B13" t="n">
         <v>57950</v>
@@ -1980,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579484</v>
+        <v>579427</v>
       </c>
       <c r="R13" t="n">
-        <v>6398383</v>
+        <v>6398257</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2015,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,13 +2036,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610366</t>
+          <t>https://artportalen.se/Sighting/118609828</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118610712</v>
+        <v>118610366</v>
       </c>
       <c r="B14" t="n">
         <v>57950</v>
@@ -2097,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579433</v>
+        <v>579484</v>
       </c>
       <c r="R14" t="n">
-        <v>6398430</v>
+        <v>6398383</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2132,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,13 +2153,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610712</t>
+          <t>https://artportalen.se/Sighting/118610366</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118611275</v>
+        <v>118610712</v>
       </c>
       <c r="B15" t="n">
         <v>57950</v>
@@ -2203,19 +2188,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kammartorp, Kammartorp, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579275</v>
+        <v>579433</v>
       </c>
       <c r="R15" t="n">
-        <v>6398015</v>
+        <v>6398430</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2244,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,13 +2270,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611275</t>
+          <t>https://artportalen.se/Sighting/118610712</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118847687</v>
+        <v>118611275</v>
       </c>
       <c r="B16" t="n">
         <v>57950</v>
@@ -2314,32 +2304,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>Kammartorp, Kammartorp, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579405</v>
+        <v>579275</v>
       </c>
       <c r="R16" t="n">
-        <v>6398324</v>
+        <v>6398015</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2363,12 +2341,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,24 +2371,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847687</t>
+          <t>https://artportalen.se/Sighting/118611275</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119624115</v>
+        <v>118847687</v>
       </c>
       <c r="B17" t="n">
         <v>57950</v>
@@ -2428,28 +2416,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579298</v>
+        <v>579405</v>
       </c>
       <c r="R17" t="n">
-        <v>6398158</v>
+        <v>6398324</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2473,17 +2465,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,13 +2496,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118847687</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119624139</v>
+        <v>119624115</v>
       </c>
       <c r="B18" t="n">
         <v>57950</v>
@@ -2548,7 +2535,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2558,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579421</v>
+        <v>579298</v>
       </c>
       <c r="R18" t="n">
-        <v>6398260</v>
+        <v>6398158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2585,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,50 +2611,46 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624139</t>
+          <t>https://artportalen.se/Sighting/119624115</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119608145</v>
+        <v>119624139</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2677,13 +2660,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579299</v>
+        <v>579421</v>
       </c>
       <c r="R19" t="n">
-        <v>6398361</v>
+        <v>6398260</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2707,12 +2690,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,16 +2726,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608145</t>
+          <t>https://artportalen.se/Sighting/119624139</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131740066</v>
+        <v>119608145</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,20 +2760,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579528</v>
+        <v>579299</v>
       </c>
       <c r="R20" t="n">
-        <v>6398236</v>
+        <v>6398361</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,74 +2829,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740066</t>
+          <t>https://artportalen.se/Sighting/119608145</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118564572</v>
+        <v>131740066</v>
       </c>
       <c r="B21" t="n">
-        <v>97986</v>
+        <v>58136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579210</v>
+        <v>579528</v>
       </c>
       <c r="R21" t="n">
-        <v>6398292</v>
+        <v>6398236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2923,12 +2911,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,34 +2925,37 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/131740066</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131733125</v>
+        <v>118564572</v>
       </c>
       <c r="B22" t="n">
-        <v>101403</v>
+        <v>97986</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,34 +2963,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579346</v>
+        <v>579210</v>
       </c>
       <c r="R22" t="n">
-        <v>6398047</v>
+        <v>6398292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,12 +3025,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,26 +3039,129 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118564572</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131733125</t>
         </is>
@@ -3088,6 +3190,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1590,7 +1590,7 @@
         <v>137022561</v>
       </c>
       <c r="B10" t="n">
-        <v>81138</v>
+        <v>81140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Lars Engström, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119624335</v>
+        <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>655</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,21 +715,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrum, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579317</v>
+        <v>579214</v>
       </c>
       <c r="R2" t="n">
-        <v>6398111</v>
+        <v>6398230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,16 +789,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624335</t>
+          <t>https://artportalen.se/Sighting/137091341</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119266053</v>
+        <v>119624335</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>655</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,21 +830,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579195</v>
+        <v>579317</v>
       </c>
       <c r="R3" t="n">
-        <v>6398252</v>
+        <v>6398111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,55 +903,62 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119266053</t>
+          <t>https://artportalen.se/Sighting/119624335</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118847592</v>
+        <v>119266053</v>
       </c>
       <c r="B4" t="n">
-        <v>96708</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579531</v>
+        <v>579195</v>
       </c>
       <c r="R4" t="n">
-        <v>6398442</v>
+        <v>6398252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,12 +985,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,13 +1027,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847592</t>
+          <t>https://artportalen.se/Sighting/119266053</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119266069</v>
+        <v>118847592</v>
       </c>
       <c r="B5" t="n">
         <v>96708</v>
@@ -1060,14 +1068,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27727, ankarsrum, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579282</v>
+        <v>579531</v>
       </c>
       <c r="R5" t="n">
-        <v>6398340</v>
+        <v>6398442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,22 +1102,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,62 +1134,55 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119266069</t>
+          <t>https://artportalen.se/Sighting/118847592</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119608229</v>
+        <v>119266069</v>
       </c>
       <c r="B6" t="n">
-        <v>91930</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579346</v>
+        <v>579282</v>
       </c>
       <c r="R6" t="n">
-        <v>6398406</v>
+        <v>6398340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,12 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,65 +1251,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608229</t>
+          <t>https://artportalen.se/Sighting/119266069</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105920013</v>
+        <v>137073517</v>
       </c>
       <c r="B7" t="n">
-        <v>91867</v>
+        <v>92331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5445</v>
+        <v>3008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrums säteri, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579189</v>
+        <v>579399</v>
       </c>
       <c r="R7" t="n">
-        <v>6398315</v>
+        <v>6398058</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,12 +1322,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Liggande tallåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,34 +1351,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105920013</t>
+          <t>https://artportalen.se/Sighting/137073517</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131732492</v>
+        <v>119608229</v>
       </c>
       <c r="B8" t="n">
-        <v>91932</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,34 +1385,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579297</v>
+        <v>579346</v>
       </c>
       <c r="R8" t="n">
-        <v>6398143</v>
+        <v>6398406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,12 +1450,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,72 +1464,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131732492</t>
+          <t>https://artportalen.se/Sighting/119608229</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131737000</v>
+        <v>105920013</v>
       </c>
       <c r="B9" t="n">
-        <v>75340</v>
+        <v>91867</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>5445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579356</v>
+        <v>579189</v>
       </c>
       <c r="R9" t="n">
-        <v>6398090</v>
+        <v>6398315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,17 +1564,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På ek</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,75 +1578,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737000</t>
+          <t>https://artportalen.se/Sighting/105920013</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137022561</v>
+        <v>131732492</v>
       </c>
       <c r="B10" t="n">
-        <v>81140</v>
+        <v>91932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6444</v>
+        <v>5445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579398</v>
+        <v>579297</v>
       </c>
       <c r="R10" t="n">
-        <v>6398145</v>
+        <v>6398143</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,12 +1667,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,27 +1687,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström, Gabriel Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137022561</t>
+          <t>https://artportalen.se/Sighting/131732492</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119624174</v>
+        <v>137091314</v>
       </c>
       <c r="B11" t="n">
-        <v>57966</v>
+        <v>92075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,49 +1719,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579371</v>
+        <v>579205</v>
       </c>
       <c r="R11" t="n">
-        <v>6398423</v>
+        <v>6398277</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,17 +1784,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,6 +1798,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1802,16 +1816,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624174</t>
+          <t>https://artportalen.se/Sighting/137091314</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118608477</v>
+        <v>131737000</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>75340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,42 +1833,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579312</v>
+        <v>579356</v>
       </c>
       <c r="R12" t="n">
-        <v>6398154</v>
+        <v>6398090</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,22 +1887,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,27 +1912,31 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/131737000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118609828</v>
+        <v>137022561</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>81140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,42 +1944,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6444</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579427</v>
+        <v>579398</v>
       </c>
       <c r="R13" t="n">
-        <v>6398257</v>
+        <v>6398145</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,22 +1998,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,27 +2018,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Lars Engström, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609828</t>
+          <t>https://artportalen.se/Sighting/137022561</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118610366</v>
+        <v>137073522</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>81140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,42 +2046,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6444</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579484</v>
+        <v>579392</v>
       </c>
       <c r="R14" t="n">
-        <v>6398383</v>
+        <v>6398150</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,22 +2100,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,27 +2130,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610366</t>
+          <t>https://artportalen.se/Sighting/137073522</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118610712</v>
+        <v>137074978</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>81140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,42 +2158,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6444</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579433</v>
+        <v>579392</v>
       </c>
       <c r="R15" t="n">
-        <v>6398430</v>
+        <v>6398144</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,22 +2212,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,44 +2242,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610712</t>
+          <t>https://artportalen.se/Sighting/137074978</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118611275</v>
+        <v>119624174</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2304,20 +2287,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kammartorp, Kammartorp, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579275</v>
+        <v>579371</v>
       </c>
       <c r="R16" t="n">
-        <v>6398015</v>
+        <v>6398423</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,22 +2336,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,24 +2361,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611275</t>
+          <t>https://artportalen.se/Sighting/119624174</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118847687</v>
+        <v>118608477</v>
       </c>
       <c r="B17" t="n">
         <v>57950</v>
@@ -2416,32 +2406,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579405</v>
+        <v>579312</v>
       </c>
       <c r="R17" t="n">
-        <v>6398324</v>
+        <v>6398154</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2465,12 +2448,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,24 +2478,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847687</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119624115</v>
+        <v>118609828</v>
       </c>
       <c r="B18" t="n">
         <v>57950</v>
@@ -2531,27 +2524,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579298</v>
+        <v>579427</v>
       </c>
       <c r="R18" t="n">
-        <v>6398158</v>
+        <v>6398257</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,17 +2565,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,24 +2595,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118609828</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119624139</v>
+        <v>118610366</v>
       </c>
       <c r="B19" t="n">
         <v>57950</v>
@@ -2646,27 +2641,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579421</v>
+        <v>579484</v>
       </c>
       <c r="R19" t="n">
-        <v>6398260</v>
+        <v>6398383</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2690,17 +2682,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,77 +2712,70 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624139</t>
+          <t>https://artportalen.se/Sighting/118610366</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119608145</v>
+        <v>118610712</v>
       </c>
       <c r="B20" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579299</v>
+        <v>579433</v>
       </c>
       <c r="R20" t="n">
-        <v>6398361</v>
+        <v>6398430</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2809,12 +2799,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,62 +2829,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608145</t>
+          <t>https://artportalen.se/Sighting/118610712</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131740066</v>
+        <v>118611275</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>Kammartorp, Kammartorp, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579528</v>
+        <v>579275</v>
       </c>
       <c r="R21" t="n">
-        <v>6398236</v>
+        <v>6398015</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,12 +2911,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2931,31 +2941,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740066</t>
+          <t>https://artportalen.se/Sighting/118611275</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118564572</v>
+        <v>118847687</v>
       </c>
       <c r="B22" t="n">
-        <v>97986</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,45 +2969,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579210</v>
+        <v>579405</v>
       </c>
       <c r="R22" t="n">
-        <v>6398292</v>
+        <v>6398324</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,12 +3035,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,7 +3049,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3057,16 +3066,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/118847687</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131733125</v>
+        <v>119624115</v>
       </c>
       <c r="B23" t="n">
-        <v>101403</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,34 +3083,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579346</v>
+        <v>579298</v>
       </c>
       <c r="R23" t="n">
-        <v>6398047</v>
+        <v>6398158</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3128,12 +3145,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,22 +3170,1247 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624115</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>119624139</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 27727, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>579421</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6398260</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624139</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137073539</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>579378</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6398039</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073539</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>119608145</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 27727, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>579299</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6398361</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119608145</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131740066</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kammarbogöl Nord, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>579528</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6398236</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740066</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137073518</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>579351</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6398114</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073518</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137073525</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>579388</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6398271</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073525</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137073519</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>579414</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6398049</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073519</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118564572</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>579210</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6398292</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118564572</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131733125</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137073527</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>579399</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6398099</v>
+      </c>
+      <c r="S33" t="n">
+        <v>47</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073527</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137073538</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>579470</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6398117</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073538</t>
         </is>
       </c>
     </row>
@@ -3191,6 +4438,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>137073517</v>
       </c>
       <c r="B7" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137091314</v>
       </c>
       <c r="B11" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>137022561</v>
       </c>
       <c r="B13" t="n">
-        <v>81140</v>
+        <v>81141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>137073522</v>
       </c>
       <c r="B14" t="n">
-        <v>81140</v>
+        <v>81141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>137074978</v>
       </c>
       <c r="B15" t="n">
-        <v>81140</v>
+        <v>81141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>137073527</v>
       </c>
       <c r="B33" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137073538</v>
       </c>
       <c r="B34" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>137073517</v>
       </c>
       <c r="B7" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137091314</v>
       </c>
       <c r="B11" t="n">
-        <v>92076</v>
+        <v>92082</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>137073527</v>
       </c>
       <c r="B33" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137073538</v>
       </c>
       <c r="B34" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>137073517</v>
       </c>
       <c r="B7" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137091314</v>
       </c>
       <c r="B11" t="n">
-        <v>92082</v>
+        <v>92086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>137022561</v>
       </c>
       <c r="B13" t="n">
-        <v>81141</v>
+        <v>81143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>137073522</v>
       </c>
       <c r="B14" t="n">
-        <v>81141</v>
+        <v>81143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>137074978</v>
       </c>
       <c r="B15" t="n">
-        <v>81141</v>
+        <v>81143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>137073527</v>
       </c>
       <c r="B33" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137073538</v>
       </c>
       <c r="B34" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>137073527</v>
       </c>
       <c r="B33" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137073538</v>
       </c>
       <c r="B34" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119624335</v>
+        <v>137220790</v>
       </c>
       <c r="B3" t="n">
-        <v>90801</v>
+        <v>92930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>655</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,17 +837,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrum, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579317</v>
+        <v>579451</v>
       </c>
       <c r="R3" t="n">
-        <v>6398111</v>
+        <v>6398252</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,12 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,16 +903,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624335</t>
+          <t>https://artportalen.se/Sighting/137220790</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119266053</v>
+        <v>119624335</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>90801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>655</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,21 +944,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579195</v>
+        <v>579317</v>
       </c>
       <c r="R4" t="n">
-        <v>6398252</v>
+        <v>6398111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,22 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,55 +1017,62 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119266053</t>
+          <t>https://artportalen.se/Sighting/119624335</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118847592</v>
+        <v>119266053</v>
       </c>
       <c r="B5" t="n">
-        <v>96708</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579531</v>
+        <v>579195</v>
       </c>
       <c r="R5" t="n">
-        <v>6398442</v>
+        <v>6398252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,12 +1099,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,13 +1141,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847592</t>
+          <t>https://artportalen.se/Sighting/119266053</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119266069</v>
+        <v>118847592</v>
       </c>
       <c r="B6" t="n">
         <v>96708</v>
@@ -1175,14 +1182,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27727, ankarsrum, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579282</v>
+        <v>579531</v>
       </c>
       <c r="R6" t="n">
-        <v>6398340</v>
+        <v>6398442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,22 +1216,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,16 +1248,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119266069</t>
+          <t>https://artportalen.se/Sighting/118847592</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137073517</v>
+        <v>119266069</v>
       </c>
       <c r="B7" t="n">
-        <v>92342</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,37 +1265,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3008</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579399</v>
+        <v>579282</v>
       </c>
       <c r="R7" t="n">
-        <v>6398058</v>
+        <v>6398340</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,27 +1323,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Liggande tallåga</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,82 +1347,72 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073517</t>
+          <t>https://artportalen.se/Sighting/119266069</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119608229</v>
+        <v>137073517</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>92344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>3008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579346</v>
+        <v>579399</v>
       </c>
       <c r="R8" t="n">
-        <v>6398406</v>
+        <v>6398058</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1436,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Liggande tallåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,80 +1465,79 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608229</t>
+          <t>https://artportalen.se/Sighting/137073517</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105920013</v>
+        <v>137220830</v>
       </c>
       <c r="B9" t="n">
-        <v>91867</v>
+        <v>92344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5445</v>
+        <v>3008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrums säteri, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579189</v>
+        <v>579425</v>
       </c>
       <c r="R9" t="n">
-        <v>6398315</v>
+        <v>6398304</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,12 +1564,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På torr barrklös tallåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,16 +1601,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105920013</t>
+          <t>https://artportalen.se/Sighting/137220830</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131732492</v>
+        <v>119608229</v>
       </c>
       <c r="B10" t="n">
-        <v>91932</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,34 +1618,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579297</v>
+        <v>579346</v>
       </c>
       <c r="R10" t="n">
-        <v>6398143</v>
+        <v>6398406</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,12 +1683,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,37 +1697,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131732492</t>
+          <t>https://artportalen.se/Sighting/119608229</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137091314</v>
+        <v>105920013</v>
       </c>
       <c r="B11" t="n">
-        <v>92086</v>
+        <v>91867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,14 +1763,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579205</v>
+        <v>579189</v>
       </c>
       <c r="R11" t="n">
-        <v>6398277</v>
+        <v>6398315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,12 +1797,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,51 +1829,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137091314</t>
+          <t>https://artportalen.se/Sighting/105920013</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131737000</v>
+        <v>131732492</v>
       </c>
       <c r="B12" t="n">
-        <v>75340</v>
+        <v>91932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>5445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579356</v>
+        <v>579297</v>
       </c>
       <c r="R12" t="n">
-        <v>6398090</v>
+        <v>6398143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,11 +1908,6 @@
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På ek</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1927,54 +1935,65 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737000</t>
+          <t>https://artportalen.se/Sighting/131732492</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137022561</v>
+        <v>137091314</v>
       </c>
       <c r="B13" t="n">
-        <v>81143</v>
+        <v>92088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6444</v>
+        <v>5445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579398</v>
+        <v>579205</v>
       </c>
       <c r="R13" t="n">
-        <v>6398145</v>
+        <v>6398277</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,12 +2017,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,33 +2031,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström, Gabriel Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137022561</t>
+          <t>https://artportalen.se/Sighting/137091314</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137073522</v>
+        <v>131737000</v>
       </c>
       <c r="B14" t="n">
-        <v>81143</v>
+        <v>75340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,37 +2066,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6444</v>
+        <v>6428</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579392</v>
+        <v>579356</v>
       </c>
       <c r="R14" t="n">
-        <v>6398150</v>
+        <v>6398090</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,22 +2120,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,27 +2145,31 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073522</t>
+          <t>https://artportalen.se/Sighting/131737000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137074978</v>
+        <v>137022561</v>
       </c>
       <c r="B15" t="n">
-        <v>81143</v>
+        <v>81146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,17 +2197,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579392</v>
+        <v>579398</v>
       </c>
       <c r="R15" t="n">
-        <v>6398144</v>
+        <v>6398145</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,19 +2234,9 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,77 +2251,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Lars Engström, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074978</t>
+          <t>https://artportalen.se/Sighting/137022561</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119624174</v>
+        <v>137073522</v>
       </c>
       <c r="B16" t="n">
-        <v>57966</v>
+        <v>81146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100048</v>
+        <v>6444</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579371</v>
+        <v>579392</v>
       </c>
       <c r="R16" t="n">
-        <v>6398423</v>
+        <v>6398150</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,17 +2333,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,27 +2363,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624174</t>
+          <t>https://artportalen.se/Sighting/137073522</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118608477</v>
+        <v>137074978</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>81146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,42 +2391,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6444</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579312</v>
+        <v>579392</v>
       </c>
       <c r="R17" t="n">
-        <v>6398154</v>
+        <v>6398144</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2448,22 +2445,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,44 +2475,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/137074978</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118609828</v>
+        <v>119624174</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2523,25 +2520,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579427</v>
+        <v>579371</v>
       </c>
       <c r="R18" t="n">
-        <v>6398257</v>
+        <v>6398423</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,22 +2569,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,24 +2594,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609828</t>
+          <t>https://artportalen.se/Sighting/119624174</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118610366</v>
+        <v>118608477</v>
       </c>
       <c r="B19" t="n">
         <v>57950</v>
@@ -2652,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579484</v>
+        <v>579312</v>
       </c>
       <c r="R19" t="n">
-        <v>6398383</v>
+        <v>6398154</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2687,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,13 +2722,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610366</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118610712</v>
+        <v>118609828</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2769,10 +2768,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579433</v>
+        <v>579427</v>
       </c>
       <c r="R20" t="n">
-        <v>6398430</v>
+        <v>6398257</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2804,7 +2803,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2813,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,13 +2839,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610712</t>
+          <t>https://artportalen.se/Sighting/118609828</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118611275</v>
+        <v>118610366</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2875,19 +2874,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kammartorp, Kammartorp, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579275</v>
+        <v>579484</v>
       </c>
       <c r="R21" t="n">
-        <v>6398015</v>
+        <v>6398383</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2916,7 +2920,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,13 +2956,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611275</t>
+          <t>https://artportalen.se/Sighting/118610366</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118847687</v>
+        <v>118610712</v>
       </c>
       <c r="B22" t="n">
         <v>57950</v>
@@ -2986,32 +2990,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579405</v>
+        <v>579433</v>
       </c>
       <c r="R22" t="n">
-        <v>6398324</v>
+        <v>6398430</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3035,12 +3032,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,24 +3062,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847687</t>
+          <t>https://artportalen.se/Sighting/118610712</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119624115</v>
+        <v>118611275</v>
       </c>
       <c r="B23" t="n">
         <v>57950</v>
@@ -3101,24 +3108,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammartorp, Kammartorp, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579298</v>
+        <v>579275</v>
       </c>
       <c r="R23" t="n">
-        <v>6398158</v>
+        <v>6398015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3145,17 +3144,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,24 +3174,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118611275</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119624139</v>
+        <v>118847687</v>
       </c>
       <c r="B24" t="n">
         <v>57950</v>
@@ -3215,28 +3219,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579421</v>
+        <v>579405</v>
       </c>
       <c r="R24" t="n">
-        <v>6398260</v>
+        <v>6398324</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3260,17 +3268,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,33 +3299,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624139</t>
+          <t>https://artportalen.se/Sighting/118847687</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137073539</v>
+        <v>119624115</v>
       </c>
       <c r="B25" t="n">
-        <v>58167</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3331,19 +3334,27 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579378</v>
+        <v>579298</v>
       </c>
       <c r="R25" t="n">
-        <v>6398039</v>
+        <v>6398158</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3367,27 +3378,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Upprörd varnande</t>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,61 +3403,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073539</t>
+          <t>https://artportalen.se/Sighting/119624115</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119608145</v>
+        <v>119624139</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3466,13 +3463,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579299</v>
+        <v>579421</v>
       </c>
       <c r="R26" t="n">
-        <v>6398361</v>
+        <v>6398260</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3496,12 +3493,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,16 +3529,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608145</t>
+          <t>https://artportalen.se/Sighting/119624139</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131740066</v>
+        <v>137073539</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>58167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,37 +3546,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579528</v>
+        <v>579378</v>
       </c>
       <c r="R27" t="n">
-        <v>6398236</v>
+        <v>6398039</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3598,12 +3600,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3618,69 +3635,77 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740066</t>
+          <t>https://artportalen.se/Sighting/137073539</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137073518</v>
+        <v>119608145</v>
       </c>
       <c r="B28" t="n">
-        <v>58164</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579351</v>
+        <v>579299</v>
       </c>
       <c r="R28" t="n">
-        <v>6398114</v>
+        <v>6398361</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3704,22 +3729,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,65 +3749,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073518</t>
+          <t>https://artportalen.se/Sighting/119608145</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137073525</v>
+        <v>131740066</v>
       </c>
       <c r="B29" t="n">
-        <v>58164</v>
+        <v>58136</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579388</v>
+        <v>579528</v>
       </c>
       <c r="R29" t="n">
-        <v>6398271</v>
+        <v>6398236</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3816,22 +3831,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,27 +3851,31 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073525</t>
+          <t>https://artportalen.se/Sighting/131740066</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137073519</v>
+        <v>137073518</v>
       </c>
       <c r="B30" t="n">
-        <v>58629</v>
+        <v>58164</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3883,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3907,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579414</v>
+        <v>579351</v>
       </c>
       <c r="R30" t="n">
-        <v>6398049</v>
+        <v>6398114</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3933,7 +3942,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3943,7 +3952,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,16 +3978,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073519</t>
+          <t>https://artportalen.se/Sighting/137073518</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118564572</v>
+        <v>137073525</v>
       </c>
       <c r="B31" t="n">
-        <v>97986</v>
+        <v>58164</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3986,45 +3995,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221946</v>
+        <v>103023</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579210</v>
+        <v>579388</v>
       </c>
       <c r="R31" t="n">
-        <v>6398292</v>
+        <v>6398271</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4048,12 +4049,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,34 +4073,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/137073525</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131733125</v>
+        <v>137073519</v>
       </c>
       <c r="B32" t="n">
-        <v>101403</v>
+        <v>58629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,37 +4107,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>103041</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>579346</v>
+        <v>579414</v>
       </c>
       <c r="R32" t="n">
-        <v>6398047</v>
+        <v>6398049</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4151,12 +4161,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,31 +4191,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131733125</t>
+          <t>https://artportalen.se/Sighting/137073519</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137073527</v>
+        <v>118564572</v>
       </c>
       <c r="B33" t="n">
-        <v>101584</v>
+        <v>97986</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4203,37 +4219,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579399</v>
+        <v>579210</v>
       </c>
       <c r="R33" t="n">
-        <v>6398099</v>
+        <v>6398292</v>
       </c>
       <c r="S33" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,22 +4281,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,33 +4295,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073527</t>
+          <t>https://artportalen.se/Sighting/118564572</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137073538</v>
+        <v>131733125</v>
       </c>
       <c r="B34" t="n">
-        <v>101584</v>
+        <v>101403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4335,17 +4350,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>579470</v>
+        <v>579346</v>
       </c>
       <c r="R34" t="n">
-        <v>6398117</v>
+        <v>6398047</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4369,22 +4384,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,16 +4404,244 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733125</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137073527</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101586</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>579399</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6398099</v>
+      </c>
+      <c r="S35" t="n">
+        <v>47</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr">
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073527</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137073538</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101586</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>579470</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6398117</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137073538</t>
         </is>
@@ -4449,6 +4682,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137220790</v>
       </c>
       <c r="B3" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137073517</v>
       </c>
       <c r="B8" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>137220830</v>
       </c>
       <c r="B9" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137091314</v>
       </c>
       <c r="B13" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>137022561</v>
       </c>
       <c r="B15" t="n">
-        <v>81146</v>
+        <v>81159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137073522</v>
       </c>
       <c r="B16" t="n">
-        <v>81146</v>
+        <v>81159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137074978</v>
       </c>
       <c r="B17" t="n">
-        <v>81146</v>
+        <v>81159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>137073539</v>
       </c>
       <c r="B27" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>137073518</v>
       </c>
       <c r="B30" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>137073525</v>
       </c>
       <c r="B31" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>137073519</v>
       </c>
       <c r="B32" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137073527</v>
       </c>
       <c r="B35" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>137073538</v>
       </c>
       <c r="B36" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137220790</v>
       </c>
       <c r="B3" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137073517</v>
       </c>
       <c r="B8" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>137220830</v>
       </c>
       <c r="B9" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137091314</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>137022561</v>
       </c>
       <c r="B15" t="n">
-        <v>81159</v>
+        <v>81161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137073522</v>
       </c>
       <c r="B16" t="n">
-        <v>81159</v>
+        <v>81161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137074978</v>
       </c>
       <c r="B17" t="n">
-        <v>81159</v>
+        <v>81161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>137073539</v>
       </c>
       <c r="B27" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>137073518</v>
       </c>
       <c r="B30" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>137073525</v>
       </c>
       <c r="B31" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>137073519</v>
       </c>
       <c r="B32" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137073527</v>
       </c>
       <c r="B35" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>137073538</v>
       </c>
       <c r="B36" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,32 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137220790</v>
+        <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>92945</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579451</v>
+        <v>579373</v>
       </c>
       <c r="R3" t="n">
-        <v>6398252</v>
+        <v>6398136</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,12 +872,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Säkert fler, men svåra!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,16 +909,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220790</t>
+          <t>https://artportalen.se/Sighting/137269259</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119624335</v>
+        <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>90801</v>
+        <v>92945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>655</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,17 +957,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrum, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579317</v>
+        <v>579451</v>
       </c>
       <c r="R4" t="n">
-        <v>6398111</v>
+        <v>6398252</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,16 +1023,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624335</t>
+          <t>https://artportalen.se/Sighting/137220790</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119266053</v>
+        <v>119624335</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>90801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>655</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,21 +1064,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579195</v>
+        <v>579317</v>
       </c>
       <c r="R5" t="n">
-        <v>6398252</v>
+        <v>6398111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,22 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,55 +1137,62 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119266053</t>
+          <t>https://artportalen.se/Sighting/119624335</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847592</v>
+        <v>119266053</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579531</v>
+        <v>579195</v>
       </c>
       <c r="R6" t="n">
-        <v>6398442</v>
+        <v>6398252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,12 +1219,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,13 +1261,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847592</t>
+          <t>https://artportalen.se/Sighting/119266053</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119266069</v>
+        <v>118847592</v>
       </c>
       <c r="B7" t="n">
         <v>96708</v>
@@ -1289,14 +1302,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27727, ankarsrum, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579282</v>
+        <v>579531</v>
       </c>
       <c r="R7" t="n">
-        <v>6398340</v>
+        <v>6398442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,22 +1336,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,16 +1368,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119266069</t>
+          <t>https://artportalen.se/Sighting/118847592</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137073517</v>
+        <v>119266069</v>
       </c>
       <c r="B8" t="n">
-        <v>92359</v>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,37 +1385,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3008</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579399</v>
+        <v>579282</v>
       </c>
       <c r="R8" t="n">
-        <v>6398058</v>
+        <v>6398340</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,27 +1443,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Liggande tallåga</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,30 +1467,31 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073517</t>
+          <t>https://artportalen.se/Sighting/119266069</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137220830</v>
+        <v>137073517</v>
       </c>
       <c r="B9" t="n">
         <v>92359</v>
@@ -1516,31 +1519,20 @@
           <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579425</v>
+        <v>579399</v>
       </c>
       <c r="R9" t="n">
-        <v>6398304</v>
+        <v>6398058</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,17 +1556,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På torr barrklös tallåga.</t>
+          <t>Liggande tallåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,56 +1585,55 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220830</t>
+          <t>https://artportalen.se/Sighting/137073517</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119608229</v>
+        <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>91930</v>
+        <v>92359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>3008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1642,21 +1643,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579346</v>
+        <v>579425</v>
       </c>
       <c r="R10" t="n">
-        <v>6398406</v>
+        <v>6398304</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,12 +1684,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På torr barrklös tallåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,16 +1721,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608229</t>
+          <t>https://artportalen.se/Sighting/137220830</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105920013</v>
+        <v>119608229</v>
       </c>
       <c r="B11" t="n">
-        <v>91867</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,26 +1738,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1763,14 +1769,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrums säteri, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579189</v>
+        <v>579346</v>
       </c>
       <c r="R11" t="n">
-        <v>6398315</v>
+        <v>6398406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,12 +1803,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,16 +1835,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105920013</t>
+          <t>https://artportalen.se/Sighting/119608229</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131732492</v>
+        <v>105920013</v>
       </c>
       <c r="B12" t="n">
-        <v>91932</v>
+        <v>91867</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,17 +1869,28 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579297</v>
+        <v>579189</v>
       </c>
       <c r="R12" t="n">
-        <v>6398143</v>
+        <v>6398315</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,12 +1917,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,37 +1931,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131732492</t>
+          <t>https://artportalen.se/Sighting/105920013</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137091314</v>
+        <v>131732492</v>
       </c>
       <c r="B13" t="n">
-        <v>92103</v>
+        <v>91932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,28 +1983,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579205</v>
+        <v>579297</v>
       </c>
       <c r="R13" t="n">
-        <v>6398277</v>
+        <v>6398143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,12 +2020,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,69 +2034,83 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137091314</t>
+          <t>https://artportalen.se/Sighting/131732492</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131737000</v>
+        <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>75340</v>
+        <v>92103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6428</v>
+        <v>5445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579356</v>
+        <v>579205</v>
       </c>
       <c r="R14" t="n">
-        <v>6398090</v>
+        <v>6398277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,17 +2137,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På ek</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,37 +2151,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737000</t>
+          <t>https://artportalen.se/Sighting/137091314</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137022561</v>
+        <v>131737000</v>
       </c>
       <c r="B15" t="n">
-        <v>81161</v>
+        <v>75340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,37 +2186,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6444</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579398</v>
+        <v>579356</v>
       </c>
       <c r="R15" t="n">
-        <v>6398145</v>
+        <v>6398090</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,12 +2240,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,24 +2265,28 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Engström, Gabriel Johansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137022561</t>
+          <t>https://artportalen.se/Sighting/131737000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137073522</v>
+        <v>137022561</v>
       </c>
       <c r="B16" t="n">
         <v>81161</v>
@@ -2299,17 +2317,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579392</v>
+        <v>579398</v>
       </c>
       <c r="R16" t="n">
-        <v>6398150</v>
+        <v>6398145</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,19 +2354,9 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,24 +2371,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Lars Engström, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073522</t>
+          <t>https://artportalen.se/Sighting/137022561</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137074978</v>
+        <v>137073522</v>
       </c>
       <c r="B17" t="n">
         <v>81161</v>
@@ -2411,17 +2419,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ankarsrum, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
         <v>579392</v>
       </c>
       <c r="R17" t="n">
-        <v>6398144</v>
+        <v>6398150</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2475,77 +2483,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074978</t>
+          <t>https://artportalen.se/Sighting/137073522</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119624174</v>
+        <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>57966</v>
+        <v>81161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>6444</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579371</v>
+        <v>579392</v>
       </c>
       <c r="R18" t="n">
-        <v>6398423</v>
+        <v>6398144</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2569,17 +2565,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,44 +2595,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624174</t>
+          <t>https://artportalen.se/Sighting/137074978</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118608477</v>
+        <v>119624174</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2639,25 +2640,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579312</v>
+        <v>579371</v>
       </c>
       <c r="R19" t="n">
-        <v>6398154</v>
+        <v>6398423</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,22 +2689,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,24 +2714,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/119624174</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118609828</v>
+        <v>118608477</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2768,10 +2771,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579427</v>
+        <v>579312</v>
       </c>
       <c r="R20" t="n">
-        <v>6398257</v>
+        <v>6398154</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2803,7 +2806,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2813,7 +2816,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,13 +2842,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609828</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118610366</v>
+        <v>118609828</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2885,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579484</v>
+        <v>579427</v>
       </c>
       <c r="R21" t="n">
-        <v>6398383</v>
+        <v>6398257</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2920,7 +2923,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2930,7 +2933,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,13 +2959,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610366</t>
+          <t>https://artportalen.se/Sighting/118609828</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118610712</v>
+        <v>118610366</v>
       </c>
       <c r="B22" t="n">
         <v>57950</v>
@@ -3002,10 +3005,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579433</v>
+        <v>579484</v>
       </c>
       <c r="R22" t="n">
-        <v>6398430</v>
+        <v>6398383</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3037,7 +3040,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3050,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,13 +3076,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610712</t>
+          <t>https://artportalen.se/Sighting/118610366</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118611275</v>
+        <v>118610712</v>
       </c>
       <c r="B23" t="n">
         <v>57950</v>
@@ -3108,19 +3111,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kammartorp, Kammartorp, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579275</v>
+        <v>579433</v>
       </c>
       <c r="R23" t="n">
-        <v>6398015</v>
+        <v>6398430</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,7 +3157,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3167,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3185,13 +3193,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611275</t>
+          <t>https://artportalen.se/Sighting/118610712</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118847687</v>
+        <v>118611275</v>
       </c>
       <c r="B24" t="n">
         <v>57950</v>
@@ -3219,32 +3227,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>Kammartorp, Kammartorp, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579405</v>
+        <v>579275</v>
       </c>
       <c r="R24" t="n">
-        <v>6398324</v>
+        <v>6398015</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3268,12 +3264,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3288,24 +3294,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847687</t>
+          <t>https://artportalen.se/Sighting/118611275</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119624115</v>
+        <v>118847687</v>
       </c>
       <c r="B25" t="n">
         <v>57950</v>
@@ -3333,28 +3339,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579298</v>
+        <v>579405</v>
       </c>
       <c r="R25" t="n">
-        <v>6398158</v>
+        <v>6398324</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,17 +3388,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3414,13 +3419,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118847687</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119624139</v>
+        <v>119624115</v>
       </c>
       <c r="B26" t="n">
         <v>57950</v>
@@ -3453,7 +3458,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579421</v>
+        <v>579298</v>
       </c>
       <c r="R26" t="n">
-        <v>6398260</v>
+        <v>6398158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3508,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,33 +3534,33 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624139</t>
+          <t>https://artportalen.se/Sighting/119624115</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137073539</v>
+        <v>119624139</v>
       </c>
       <c r="B27" t="n">
-        <v>58182</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3564,19 +3569,27 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579378</v>
+        <v>579421</v>
       </c>
       <c r="R27" t="n">
-        <v>6398039</v>
+        <v>6398260</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3600,27 +3613,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Upprörd varnande</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,77 +3638,69 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073539</t>
+          <t>https://artportalen.se/Sighting/119624139</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119608145</v>
+        <v>137269219</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>58020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579299</v>
+        <v>579353</v>
       </c>
       <c r="R28" t="n">
-        <v>6398361</v>
+        <v>6398156</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3729,12 +3724,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2 relativt färska bohål i grov asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,51 +3760,55 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608145</t>
+          <t>https://artportalen.se/Sighting/137269219</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131740066</v>
+        <v>137269343</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>58020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579528</v>
+        <v>579372</v>
       </c>
       <c r="R29" t="n">
-        <v>6398236</v>
+        <v>6398152</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3831,12 +3835,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bearbetat murken låga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,31 +3860,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740066</t>
+          <t>https://artportalen.se/Sighting/137269343</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137073518</v>
+        <v>137269366</v>
       </c>
       <c r="B30" t="n">
-        <v>58179</v>
+        <v>58020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,16 +3888,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3900,20 +3905,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579351</v>
+        <v>579370</v>
       </c>
       <c r="R30" t="n">
-        <v>6398114</v>
+        <v>6398175</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3937,22 +3950,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3967,44 +3970,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073518</t>
+          <t>https://artportalen.se/Sighting/137269366</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137073525</v>
+        <v>137073539</v>
       </c>
       <c r="B31" t="n">
-        <v>58179</v>
+        <v>58182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103023</v>
+        <v>103020</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4019,10 +4022,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579388</v>
+        <v>579378</v>
       </c>
       <c r="R31" t="n">
-        <v>6398271</v>
+        <v>6398039</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4054,7 +4057,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4064,7 +4067,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4090,54 +4098,66 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073525</t>
+          <t>https://artportalen.se/Sighting/137073539</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137073519</v>
+        <v>119608145</v>
       </c>
       <c r="B32" t="n">
-        <v>58644</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103041</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>579414</v>
+        <v>579299</v>
       </c>
       <c r="R32" t="n">
-        <v>6398049</v>
+        <v>6398361</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4161,22 +4181,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4191,70 +4201,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073519</t>
+          <t>https://artportalen.se/Sighting/119608145</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118564572</v>
+        <v>131740066</v>
       </c>
       <c r="B33" t="n">
-        <v>97986</v>
+        <v>58136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579210</v>
+        <v>579528</v>
       </c>
       <c r="R33" t="n">
-        <v>6398292</v>
+        <v>6398236</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4281,12 +4283,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4295,72 +4297,83 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/131740066</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131733125</v>
+        <v>137269124</v>
       </c>
       <c r="B34" t="n">
-        <v>101403</v>
+        <v>58184</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>579346</v>
+        <v>579207</v>
       </c>
       <c r="R34" t="n">
-        <v>6398047</v>
+        <v>6398281</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4384,12 +4397,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,31 +4417,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131733125</t>
+          <t>https://artportalen.se/Sighting/137269124</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137073527</v>
+        <v>137073518</v>
       </c>
       <c r="B35" t="n">
-        <v>101601</v>
+        <v>58179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,21 +4445,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4460,13 +4469,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>579399</v>
+        <v>579351</v>
       </c>
       <c r="R35" t="n">
-        <v>6398099</v>
+        <v>6398114</v>
       </c>
       <c r="S35" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4495,7 +4504,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4505,7 +4514,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4531,16 +4540,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073527</t>
+          <t>https://artportalen.se/Sighting/137073518</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137073538</v>
+        <v>137073525</v>
       </c>
       <c r="B36" t="n">
-        <v>101601</v>
+        <v>58179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4548,21 +4557,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>103023</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4572,10 +4581,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>579470</v>
+        <v>579388</v>
       </c>
       <c r="R36" t="n">
-        <v>6398117</v>
+        <v>6398271</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4607,7 +4616,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4617,7 +4626,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4642,6 +4651,670 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073525</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137073519</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58644</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>579414</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6398049</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073519</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137269493</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>A 27727, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>579443</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6398302</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137269493</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118564572</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>579210</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6398292</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118564572</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733125</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137073527</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>579399</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6398099</v>
+      </c>
+      <c r="S41" t="n">
+        <v>47</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073527</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137073538</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>579470</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6398117</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137073538</t>
         </is>
@@ -4684,6 +5357,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137073527</v>
       </c>
       <c r="B41" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>137073538</v>
       </c>
       <c r="B42" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92106</v>
+        <v>92116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137022561</v>
       </c>
       <c r="B16" t="n">
-        <v>81161</v>
+        <v>81171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137073522</v>
       </c>
       <c r="B17" t="n">
-        <v>81161</v>
+        <v>81171</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>81161</v>
+        <v>81171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>137269219</v>
       </c>
       <c r="B28" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>137269343</v>
       </c>
       <c r="B29" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>137269366</v>
       </c>
       <c r="B30" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>137073539</v>
       </c>
       <c r="B31" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137269124</v>
       </c>
       <c r="B34" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>137073518</v>
       </c>
       <c r="B35" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>137073525</v>
       </c>
       <c r="B36" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>137073519</v>
       </c>
       <c r="B37" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>137269493</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137073527</v>
       </c>
       <c r="B41" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>137073538</v>
       </c>
       <c r="B42" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>137269493</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137073527</v>
       </c>
       <c r="B41" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>137073538</v>
       </c>
       <c r="B42" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2731,27 +2731,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118608477</v>
+        <v>137342625</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>58046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2760,24 +2760,20 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+          <t>Kärren, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579312</v>
+        <v>579175</v>
       </c>
       <c r="R20" t="n">
-        <v>6398154</v>
+        <v>6398194</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2801,22 +2797,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2831,24 +2827,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608477</t>
+          <t>https://artportalen.se/Sighting/137342625</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118609828</v>
+        <v>118608477</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2888,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579427</v>
+        <v>579312</v>
       </c>
       <c r="R21" t="n">
-        <v>6398257</v>
+        <v>6398154</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2923,7 +2919,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2933,7 +2929,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,13 +2955,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609828</t>
+          <t>https://artportalen.se/Sighting/118608477</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118610366</v>
+        <v>118609828</v>
       </c>
       <c r="B22" t="n">
         <v>57950</v>
@@ -3005,10 +3001,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579484</v>
+        <v>579427</v>
       </c>
       <c r="R22" t="n">
-        <v>6398383</v>
+        <v>6398257</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3040,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3050,7 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,13 +3072,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610366</t>
+          <t>https://artportalen.se/Sighting/118609828</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118610712</v>
+        <v>118610366</v>
       </c>
       <c r="B23" t="n">
         <v>57950</v>
@@ -3122,10 +3118,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579433</v>
+        <v>579484</v>
       </c>
       <c r="R23" t="n">
-        <v>6398430</v>
+        <v>6398383</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3157,7 +3153,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3167,7 +3163,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,13 +3189,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610712</t>
+          <t>https://artportalen.se/Sighting/118610366</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118611275</v>
+        <v>118610712</v>
       </c>
       <c r="B24" t="n">
         <v>57950</v>
@@ -3228,19 +3224,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kammartorp, Kammartorp, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579275</v>
+        <v>579433</v>
       </c>
       <c r="R24" t="n">
-        <v>6398015</v>
+        <v>6398430</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3269,7 +3270,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3279,7 +3280,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,13 +3306,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611275</t>
+          <t>https://artportalen.se/Sighting/118610712</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118847687</v>
+        <v>118611275</v>
       </c>
       <c r="B25" t="n">
         <v>57950</v>
@@ -3339,32 +3340,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>Kammartorp, Kammartorp, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579405</v>
+        <v>579275</v>
       </c>
       <c r="R25" t="n">
-        <v>6398324</v>
+        <v>6398015</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,12 +3377,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,24 +3407,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847687</t>
+          <t>https://artportalen.se/Sighting/118611275</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119624115</v>
+        <v>118847687</v>
       </c>
       <c r="B26" t="n">
         <v>57950</v>
@@ -3453,28 +3452,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579298</v>
+        <v>579405</v>
       </c>
       <c r="R26" t="n">
-        <v>6398158</v>
+        <v>6398324</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,17 +3501,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,13 +3532,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624115</t>
+          <t>https://artportalen.se/Sighting/118847687</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119624139</v>
+        <v>119624115</v>
       </c>
       <c r="B27" t="n">
         <v>57950</v>
@@ -3573,7 +3571,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3583,10 +3581,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579421</v>
+        <v>579298</v>
       </c>
       <c r="R27" t="n">
-        <v>6398260</v>
+        <v>6398158</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3623,7 +3621,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,16 +3647,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624139</t>
+          <t>https://artportalen.se/Sighting/119624115</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137269219</v>
+        <v>119624139</v>
       </c>
       <c r="B28" t="n">
-        <v>58030</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3686,18 +3684,22 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579353</v>
+        <v>579421</v>
       </c>
       <c r="R28" t="n">
-        <v>6398156</v>
+        <v>6398260</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,17 +3726,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2 relativt färska bohål i grov asp</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,13 +3762,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137269219</t>
+          <t>https://artportalen.se/Sighting/119624139</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137269343</v>
+        <v>137269219</v>
       </c>
       <c r="B29" t="n">
         <v>58030</v>
@@ -3805,10 +3807,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579372</v>
+        <v>579353</v>
       </c>
       <c r="R29" t="n">
-        <v>6398152</v>
+        <v>6398156</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3845,7 +3847,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Bearbetat murken låga</t>
+          <t>2 relativt färska bohål i grov asp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3871,13 +3873,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137269343</t>
+          <t>https://artportalen.se/Sighting/137269219</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137269366</v>
+        <v>137269343</v>
       </c>
       <c r="B30" t="n">
         <v>58030</v>
@@ -3905,11 +3907,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -3920,13 +3918,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579370</v>
+        <v>579372</v>
       </c>
       <c r="R30" t="n">
-        <v>6398175</v>
+        <v>6398152</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3956,6 +3954,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bearbetat murken låga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,33 +3984,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137269366</t>
+          <t>https://artportalen.se/Sighting/137269343</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137073539</v>
+        <v>137269366</v>
       </c>
       <c r="B31" t="n">
-        <v>58192</v>
+        <v>58030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4015,20 +4018,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579378</v>
+        <v>579370</v>
       </c>
       <c r="R31" t="n">
-        <v>6398039</v>
+        <v>6398175</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4052,27 +4063,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4087,27 +4083,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073539</t>
+          <t>https://artportalen.se/Sighting/137269366</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119608145</v>
+        <v>137073539</v>
       </c>
       <c r="B32" t="n">
-        <v>58114</v>
+        <v>58192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4115,49 +4111,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>579299</v>
+        <v>579378</v>
       </c>
       <c r="R32" t="n">
-        <v>6398361</v>
+        <v>6398039</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4181,12 +4165,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4201,27 +4200,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119608145</t>
+          <t>https://artportalen.se/Sighting/137073539</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131740066</v>
+        <v>119608145</v>
       </c>
       <c r="B33" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4246,20 +4245,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579528</v>
+        <v>579299</v>
       </c>
       <c r="R33" t="n">
-        <v>6398236</v>
+        <v>6398361</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4283,12 +4294,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,31 +4314,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740066</t>
+          <t>https://artportalen.se/Sighting/119608145</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137269124</v>
+        <v>131740066</v>
       </c>
       <c r="B34" t="n">
-        <v>58194</v>
+        <v>58136</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,28 +4359,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>579207</v>
+        <v>579528</v>
       </c>
       <c r="R34" t="n">
-        <v>6398281</v>
+        <v>6398236</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4397,12 +4396,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,65 +4416,77 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137269124</t>
+          <t>https://artportalen.se/Sighting/131740066</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137073518</v>
+        <v>137269124</v>
       </c>
       <c r="B35" t="n">
-        <v>58189</v>
+        <v>58194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>579351</v>
+        <v>579207</v>
       </c>
       <c r="R35" t="n">
-        <v>6398114</v>
+        <v>6398281</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4499,22 +4510,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4529,24 +4530,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073518</t>
+          <t>https://artportalen.se/Sighting/137269124</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137073525</v>
+        <v>137073518</v>
       </c>
       <c r="B36" t="n">
         <v>58189</v>
@@ -4581,10 +4582,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>579388</v>
+        <v>579351</v>
       </c>
       <c r="R36" t="n">
-        <v>6398271</v>
+        <v>6398114</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4616,7 +4617,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4626,7 +4627,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4652,16 +4653,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073525</t>
+          <t>https://artportalen.se/Sighting/137073518</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137073519</v>
+        <v>137073525</v>
       </c>
       <c r="B37" t="n">
-        <v>58654</v>
+        <v>58189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4669,21 +4670,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4693,10 +4694,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>579414</v>
+        <v>579388</v>
       </c>
       <c r="R37" t="n">
-        <v>6398049</v>
+        <v>6398271</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4728,7 +4729,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4738,7 +4739,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4764,62 +4765,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073519</t>
+          <t>https://artportalen.se/Sighting/137073525</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137269493</v>
+        <v>137073519</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>58654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103041</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>579443</v>
+        <v>579414</v>
       </c>
       <c r="R38" t="n">
-        <v>6398302</v>
+        <v>6398049</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4843,12 +4836,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4857,56 +4860,55 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137269493</t>
+          <t>https://artportalen.se/Sighting/137073519</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118564572</v>
+        <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>97986</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4920,14 +4922,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>579210</v>
+        <v>579443</v>
       </c>
       <c r="R39" t="n">
-        <v>6398292</v>
+        <v>6398302</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4954,12 +4956,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4986,16 +4988,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118564572</t>
+          <t>https://artportalen.se/Sighting/137269493</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131733125</v>
+        <v>118564572</v>
       </c>
       <c r="B40" t="n">
-        <v>101403</v>
+        <v>97986</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5003,34 +5005,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>579346</v>
+        <v>579210</v>
       </c>
       <c r="R40" t="n">
-        <v>6398047</v>
+        <v>6398292</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5057,12 +5067,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5071,37 +5081,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131733125</t>
+          <t>https://artportalen.se/Sighting/118564572</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137073527</v>
+        <v>131733125</v>
       </c>
       <c r="B41" t="n">
-        <v>101620</v>
+        <v>101403</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5129,17 +5136,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ankarsrum tallriterevir, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>579399</v>
+        <v>579346</v>
       </c>
       <c r="R41" t="n">
-        <v>6398099</v>
+        <v>6398047</v>
       </c>
       <c r="S41" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5163,22 +5170,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,24 +5190,28 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073527</t>
+          <t>https://artportalen.se/Sighting/131733125</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137073538</v>
+        <v>137073527</v>
       </c>
       <c r="B42" t="n">
         <v>101620</v>
@@ -5245,13 +5246,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>579470</v>
+        <v>579399</v>
       </c>
       <c r="R42" t="n">
-        <v>6398117</v>
+        <v>6398099</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5280,7 +5281,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5290,7 +5291,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,6 +5316,118 @@
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073527</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137073538</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>579470</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6398117</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137073538</t>
         </is>
@@ -5363,6 +5476,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>92120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137022561</v>
       </c>
       <c r="B16" t="n">
-        <v>81171</v>
+        <v>81174</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137073522</v>
       </c>
       <c r="B17" t="n">
-        <v>81171</v>
+        <v>81174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>81171</v>
+        <v>81174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137342625</v>
       </c>
       <c r="B20" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>137269219</v>
       </c>
       <c r="B29" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>137269343</v>
       </c>
       <c r="B30" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137269366</v>
       </c>
       <c r="B31" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>137073539</v>
       </c>
       <c r="B32" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>137269124</v>
       </c>
       <c r="B35" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>137073518</v>
       </c>
       <c r="B36" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>137073525</v>
       </c>
       <c r="B37" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137073519</v>
       </c>
       <c r="B38" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>137073527</v>
       </c>
       <c r="B42" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>137073538</v>
       </c>
       <c r="B43" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>137073527</v>
       </c>
       <c r="B42" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>137073538</v>
       </c>
       <c r="B43" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92122</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137022561</v>
       </c>
       <c r="B16" t="n">
-        <v>81174</v>
+        <v>81179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137073522</v>
       </c>
       <c r="B17" t="n">
-        <v>81174</v>
+        <v>81179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>81174</v>
+        <v>81179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137342625</v>
       </c>
       <c r="B20" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>137269219</v>
       </c>
       <c r="B29" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>137269343</v>
       </c>
       <c r="B30" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137269366</v>
       </c>
       <c r="B31" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>137073539</v>
       </c>
       <c r="B32" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>137269124</v>
       </c>
       <c r="B35" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>137073518</v>
       </c>
       <c r="B36" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>137073525</v>
       </c>
       <c r="B37" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137073519</v>
       </c>
       <c r="B38" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>137073527</v>
       </c>
       <c r="B42" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>137073538</v>
       </c>
       <c r="B43" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137022561</v>
       </c>
       <c r="B16" t="n">
-        <v>81179</v>
+        <v>81190</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137073522</v>
       </c>
       <c r="B17" t="n">
-        <v>81179</v>
+        <v>81190</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>81179</v>
+        <v>81190</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>137073527</v>
       </c>
       <c r="B42" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>137073538</v>
       </c>
       <c r="B43" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137022561</v>
       </c>
       <c r="B16" t="n">
-        <v>81190</v>
+        <v>81191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137073522</v>
       </c>
       <c r="B17" t="n">
-        <v>81190</v>
+        <v>81191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>81190</v>
+        <v>81191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>137073527</v>
       </c>
       <c r="B42" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>137073538</v>
       </c>
       <c r="B43" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137022561</v>
       </c>
       <c r="B16" t="n">
-        <v>81191</v>
+        <v>81193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137073522</v>
       </c>
       <c r="B17" t="n">
-        <v>81191</v>
+        <v>81193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>81191</v>
+        <v>81193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>137073527</v>
       </c>
       <c r="B42" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>137073538</v>
       </c>
       <c r="B43" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091341</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137269259</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>137220790</v>
       </c>
       <c r="B4" t="n">
-        <v>92985</v>
+        <v>92989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137073517</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137220830</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137091314</v>
       </c>
       <c r="B14" t="n">
-        <v>92143</v>
+        <v>92147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137022561</v>
       </c>
       <c r="B16" t="n">
-        <v>81193</v>
+        <v>81197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137073522</v>
       </c>
       <c r="B17" t="n">
-        <v>81193</v>
+        <v>81197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137074978</v>
       </c>
       <c r="B18" t="n">
-        <v>81193</v>
+        <v>81197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137342625</v>
       </c>
       <c r="B20" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>137269219</v>
       </c>
       <c r="B29" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>137269343</v>
       </c>
       <c r="B30" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137269366</v>
       </c>
       <c r="B31" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>137073539</v>
       </c>
       <c r="B32" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>137269124</v>
       </c>
       <c r="B35" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>137073518</v>
       </c>
       <c r="B36" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>137073525</v>
       </c>
       <c r="B37" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137073519</v>
       </c>
       <c r="B38" t="n">
-        <v>58658</v>
+        <v>58661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>137269493</v>
       </c>
       <c r="B39" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>137073527</v>
       </c>
       <c r="B42" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>137073538</v>
       </c>
       <c r="B43" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
